--- a/uploads/Flowers by Khansa Oktober 2024.xlsx
+++ b/uploads/Flowers by Khansa Oktober 2024.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\App\Xampp\htdocs\prototype-penjualan-bunga\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E087485C-A5DD-4A00-B533-8D4BDF0FF2A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FEE2CCC-7EF7-4008-AEB4-042563ECE23C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="19200" windowHeight="10300" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PEKAN 1" sheetId="2" r:id="rId1"/>
@@ -738,17 +738,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F108"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="13.3828125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.4140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="10.23046875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.4609375" customWidth="1"/>
-    <col min="5" max="5" width="17.69140625" customWidth="1"/>
-    <col min="6" max="6" width="20.15234375" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" customWidth="1"/>
+    <col min="4" max="4" width="17.5" customWidth="1"/>
+    <col min="5" max="5" width="17.6640625" customWidth="1"/>
+    <col min="6" max="6" width="20.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -768,7 +768,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -787,7 +787,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -806,7 +806,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -825,7 +825,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -844,7 +844,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -863,7 +863,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -882,7 +882,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -901,7 +901,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -920,7 +920,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -939,7 +939,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -958,7 +958,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A12" s="5">
         <v>11</v>
       </c>
@@ -977,7 +977,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A13" s="5">
         <v>12</v>
       </c>
@@ -996,7 +996,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A14" s="5">
         <v>13</v>
       </c>
@@ -1015,7 +1015,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15" s="5">
         <v>14</v>
       </c>
@@ -1034,7 +1034,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16" s="5">
         <v>15</v>
       </c>
@@ -1053,7 +1053,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17" s="5">
         <v>16</v>
       </c>
@@ -1072,7 +1072,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A18" s="5">
         <v>17</v>
       </c>
@@ -1091,7 +1091,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A19" s="5">
         <v>18</v>
       </c>
@@ -1110,7 +1110,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A20" s="5">
         <v>19</v>
       </c>
@@ -1129,7 +1129,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A21" s="5">
         <v>20</v>
       </c>
@@ -1148,7 +1148,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A22" s="5">
         <v>21</v>
       </c>
@@ -1167,7 +1167,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A23" s="5">
         <v>22</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>1714</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A24" s="5">
         <v>23</v>
       </c>
@@ -1205,7 +1205,7 @@
         <v>1741</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A25" s="5">
         <v>24</v>
       </c>
@@ -1224,7 +1224,7 @@
         <v>1944</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A26" s="5">
         <v>25</v>
       </c>
@@ -1243,7 +1243,7 @@
         <v>1974</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A27" s="5">
         <v>26</v>
       </c>
@@ -1262,7 +1262,7 @@
         <v>2059</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A28" s="5">
         <v>27</v>
       </c>
@@ -1281,7 +1281,7 @@
         <v>2149</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A29" s="5">
         <v>28</v>
       </c>
@@ -1300,7 +1300,7 @@
         <v>2226</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A30" s="5">
         <v>29</v>
       </c>
@@ -1318,7 +1318,7 @@
         <v>2196</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31" s="5">
         <v>30</v>
       </c>
@@ -1337,7 +1337,7 @@
         <v>2257</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A32" s="5">
         <v>31</v>
       </c>
@@ -1356,7 +1356,7 @@
         <v>2295</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A33" s="5">
         <v>32</v>
       </c>
@@ -1375,7 +1375,7 @@
         <v>2310</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A34" s="5">
         <v>33</v>
       </c>
@@ -1394,7 +1394,7 @@
         <v>2330</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A35" s="5">
         <v>34</v>
       </c>
@@ -1413,7 +1413,7 @@
         <v>2360</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A36" s="5">
         <v>35</v>
       </c>
@@ -1432,7 +1432,7 @@
         <v>2560</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A37" s="5">
         <v>36</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>2610</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A38" s="5">
         <v>37</v>
       </c>
@@ -1470,7 +1470,7 @@
         <v>2535</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A39" s="5">
         <v>38</v>
       </c>
@@ -1489,7 +1489,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A40" s="5">
         <v>39</v>
       </c>
@@ -1508,7 +1508,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A41" s="5">
         <v>40</v>
       </c>
@@ -1527,7 +1527,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A42" s="5">
         <v>41</v>
       </c>
@@ -1546,7 +1546,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A43" s="5">
         <v>42</v>
       </c>
@@ -1565,7 +1565,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A44" s="5">
         <v>43</v>
       </c>
@@ -1584,7 +1584,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A45" s="5">
         <v>44</v>
       </c>
@@ -1603,7 +1603,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A46" s="5">
         <v>45</v>
       </c>
@@ -1622,7 +1622,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A47" s="5">
         <v>46</v>
       </c>
@@ -1641,7 +1641,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A48" s="5">
         <v>47</v>
       </c>
@@ -1660,7 +1660,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A49" s="5">
         <v>48</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A50" s="5">
         <v>49</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A51" s="5">
         <v>50</v>
       </c>
@@ -1717,7 +1717,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A52" s="5">
         <v>51</v>
       </c>
@@ -1736,7 +1736,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A53" s="5">
         <v>52</v>
       </c>
@@ -1755,7 +1755,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A54" s="5">
         <v>53</v>
       </c>
@@ -1774,7 +1774,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A55" s="5">
         <v>54</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A56" s="5">
         <v>55</v>
       </c>
@@ -1812,7 +1812,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A57" s="5">
         <v>56</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A58" s="5">
         <v>57</v>
       </c>
@@ -1850,7 +1850,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A59" s="5">
         <v>58</v>
       </c>
@@ -1869,7 +1869,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A60" s="5">
         <v>59</v>
       </c>
@@ -1888,7 +1888,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A61" s="5">
         <v>60</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A62" s="5">
         <v>61</v>
       </c>
@@ -1926,7 +1926,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A63" s="5">
         <v>62</v>
       </c>
@@ -1945,7 +1945,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A64" s="5">
         <v>63</v>
       </c>
@@ -1964,7 +1964,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A65" s="5">
         <v>64</v>
       </c>
@@ -1983,7 +1983,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A66" s="5">
         <v>65</v>
       </c>
@@ -2002,7 +2002,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A67" s="5">
         <v>66</v>
       </c>
@@ -2021,7 +2021,7 @@
         <v>1325</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A68" s="5">
         <v>67</v>
       </c>
@@ -2040,7 +2040,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A69" s="5">
         <v>68</v>
       </c>
@@ -2059,7 +2059,7 @@
         <v>1325</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A70" s="5">
         <v>69</v>
       </c>
@@ -2078,7 +2078,7 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A71" s="5">
         <v>70</v>
       </c>
@@ -2097,7 +2097,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A72" s="5">
         <v>71</v>
       </c>
@@ -2116,7 +2116,7 @@
         <v>1401</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A73" s="5">
         <v>72</v>
       </c>
@@ -2135,7 +2135,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A74" s="5">
         <v>73</v>
       </c>
@@ -2154,7 +2154,7 @@
         <v>1461</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A75" s="5">
         <v>74</v>
       </c>
@@ -2173,7 +2173,7 @@
         <v>1531</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A76" s="5">
         <v>75</v>
       </c>
@@ -2192,7 +2192,7 @@
         <v>1515</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A77" s="5">
         <v>76</v>
       </c>
@@ -2211,7 +2211,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A78" s="5">
         <v>77</v>
       </c>
@@ -2230,7 +2230,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A79" s="5">
         <v>78</v>
       </c>
@@ -2249,7 +2249,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A80" s="5">
         <v>79</v>
       </c>
@@ -2268,7 +2268,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A81" s="5">
         <v>80</v>
       </c>
@@ -2287,7 +2287,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A82" s="5">
         <v>81</v>
       </c>
@@ -2306,7 +2306,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A83" s="5">
         <v>82</v>
       </c>
@@ -2325,7 +2325,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A84" s="5">
         <v>83</v>
       </c>
@@ -2344,7 +2344,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A85" s="5">
         <v>84</v>
       </c>
@@ -2363,7 +2363,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A86" s="5">
         <v>85</v>
       </c>
@@ -2382,7 +2382,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A87" s="5">
         <v>86</v>
       </c>
@@ -2401,7 +2401,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A88" s="5">
         <v>87</v>
       </c>
@@ -2420,7 +2420,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A89" s="5">
         <v>88</v>
       </c>
@@ -2439,7 +2439,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A90" s="5">
         <v>89</v>
       </c>
@@ -2458,7 +2458,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A91" s="5">
         <v>90</v>
       </c>
@@ -2477,7 +2477,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A92" s="5">
         <v>91</v>
       </c>
@@ -2496,7 +2496,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A93" s="5">
         <v>92</v>
       </c>
@@ -2515,7 +2515,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A94" s="5">
         <v>93</v>
       </c>
@@ -2534,7 +2534,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A95" s="5">
         <v>94</v>
       </c>
@@ -2553,7 +2553,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A96" s="5">
         <v>95</v>
       </c>
@@ -2572,7 +2572,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A97" s="5">
         <v>96</v>
       </c>
@@ -2591,7 +2591,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A98" s="5">
         <v>97</v>
       </c>
@@ -2608,7 +2608,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A99" s="5">
         <v>98</v>
       </c>
@@ -2627,7 +2627,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A100" s="5">
         <v>99</v>
       </c>
@@ -2646,7 +2646,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A101" s="5">
         <v>100</v>
       </c>
@@ -2665,7 +2665,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A102" s="5">
         <v>101</v>
       </c>
@@ -2684,7 +2684,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A103" s="5">
         <v>102</v>
       </c>
@@ -2703,7 +2703,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A104" s="5">
         <v>103</v>
       </c>
@@ -2722,7 +2722,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A105" s="5">
         <v>104</v>
       </c>
@@ -2741,7 +2741,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A106" s="5">
         <v>105</v>
       </c>
@@ -2760,7 +2760,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A107" s="5">
         <v>106</v>
       </c>
@@ -2779,7 +2779,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A108" s="5">
         <v>107</v>
       </c>
@@ -2807,17 +2807,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F167"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="13.3828125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.4140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="12.69140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.69140625" customWidth="1"/>
-    <col min="5" max="5" width="18.61328125" customWidth="1"/>
-    <col min="6" max="6" width="15.4609375" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" customWidth="1"/>
+    <col min="5" max="5" width="18.58203125" customWidth="1"/>
+    <col min="6" max="6" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2837,7 +2837,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -2856,7 +2856,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -2875,7 +2875,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -2894,7 +2894,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -2913,7 +2913,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -2932,7 +2932,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -2951,7 +2951,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -2970,7 +2970,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -2989,7 +2989,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -3008,7 +3008,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -3027,7 +3027,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A12" s="5">
         <v>11</v>
       </c>
@@ -3046,7 +3046,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A13" s="5">
         <v>12</v>
       </c>
@@ -3065,7 +3065,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A14" s="5">
         <v>13</v>
       </c>
@@ -3084,7 +3084,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15" s="5">
         <v>14</v>
       </c>
@@ -3103,7 +3103,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16" s="5">
         <v>15</v>
       </c>
@@ -3122,7 +3122,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17" s="5">
         <v>16</v>
       </c>
@@ -3141,7 +3141,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A18" s="5">
         <v>17</v>
       </c>
@@ -3160,7 +3160,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A19" s="5">
         <v>18</v>
       </c>
@@ -3179,7 +3179,7 @@
         <v>1272</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A20" s="5">
         <v>19</v>
       </c>
@@ -3198,7 +3198,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A21" s="5">
         <v>20</v>
       </c>
@@ -3217,7 +3217,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A22" s="5">
         <v>21</v>
       </c>
@@ -3236,7 +3236,7 @@
         <v>1532</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A23" s="5">
         <v>22</v>
       </c>
@@ -3255,7 +3255,7 @@
         <v>1577</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A24" s="5">
         <v>23</v>
       </c>
@@ -3274,7 +3274,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A25" s="5">
         <v>24</v>
       </c>
@@ -3293,7 +3293,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A26" s="5">
         <v>25</v>
       </c>
@@ -3312,7 +3312,7 @@
         <v>1569</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A27" s="5">
         <v>26</v>
       </c>
@@ -3331,7 +3331,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A28" s="5">
         <v>27</v>
       </c>
@@ -3350,7 +3350,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A29" s="5">
         <v>28</v>
       </c>
@@ -3369,7 +3369,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A30" s="5">
         <v>29</v>
       </c>
@@ -3388,7 +3388,7 @@
         <v>1656</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31" s="5">
         <v>30</v>
       </c>
@@ -3407,7 +3407,7 @@
         <v>1686</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A32" s="5">
         <v>31</v>
       </c>
@@ -3426,7 +3426,7 @@
         <v>1776</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A33" s="5">
         <v>32</v>
       </c>
@@ -3445,7 +3445,7 @@
         <v>1831</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A34" s="5">
         <v>33</v>
       </c>
@@ -3464,7 +3464,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A35" s="5">
         <v>34</v>
       </c>
@@ -3483,7 +3483,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A36" s="5">
         <v>35</v>
       </c>
@@ -3502,7 +3502,7 @@
         <v>1963</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A37" s="5">
         <v>36</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>1993</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A38" s="5">
         <v>37</v>
       </c>
@@ -3540,7 +3540,7 @@
         <v>2113</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A39" s="5">
         <v>38</v>
       </c>
@@ -3559,7 +3559,7 @@
         <v>2118</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A40" s="5">
         <v>39</v>
       </c>
@@ -3578,7 +3578,7 @@
         <v>2098</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A41" s="5">
         <v>40</v>
       </c>
@@ -3597,7 +3597,7 @@
         <v>2075</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A42" s="5">
         <v>41</v>
       </c>
@@ -3616,7 +3616,7 @@
         <v>2175</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A43" s="5">
         <v>42</v>
       </c>
@@ -3635,7 +3635,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A44" s="5">
         <v>43</v>
       </c>
@@ -3654,7 +3654,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A45" s="5">
         <v>44</v>
       </c>
@@ -3673,7 +3673,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A46" s="5">
         <v>45</v>
       </c>
@@ -3692,7 +3692,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A47" s="5">
         <v>46</v>
       </c>
@@ -3711,7 +3711,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A48" s="5">
         <v>47</v>
       </c>
@@ -3730,7 +3730,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A49" s="5">
         <v>48</v>
       </c>
@@ -3749,7 +3749,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A50" s="5">
         <v>49</v>
       </c>
@@ -3768,7 +3768,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A51" s="5">
         <v>50</v>
       </c>
@@ -3787,7 +3787,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A52" s="5">
         <v>51</v>
       </c>
@@ -3806,7 +3806,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A53" s="5">
         <v>52</v>
       </c>
@@ -3825,7 +3825,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A54" s="5">
         <v>53</v>
       </c>
@@ -3844,7 +3844,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A55" s="5">
         <v>54</v>
       </c>
@@ -3863,7 +3863,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A56" s="5">
         <v>55</v>
       </c>
@@ -3882,7 +3882,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A57" s="5">
         <v>56</v>
       </c>
@@ -3901,7 +3901,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A58" s="5">
         <v>57</v>
       </c>
@@ -3920,7 +3920,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A59" s="5">
         <v>58</v>
       </c>
@@ -3939,7 +3939,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A60" s="5">
         <v>59</v>
       </c>
@@ -3958,7 +3958,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A61" s="5">
         <v>60</v>
       </c>
@@ -3977,7 +3977,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A62" s="5">
         <v>61</v>
       </c>
@@ -3996,7 +3996,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A63" s="5">
         <v>62</v>
       </c>
@@ -4015,7 +4015,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A64" s="5">
         <v>63</v>
       </c>
@@ -4034,7 +4034,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A65" s="5">
         <v>64</v>
       </c>
@@ -4053,7 +4053,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A66" s="5">
         <v>65</v>
       </c>
@@ -4072,7 +4072,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A67" s="5">
         <v>66</v>
       </c>
@@ -4091,7 +4091,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A68" s="5">
         <v>67</v>
       </c>
@@ -4110,7 +4110,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A69" s="5">
         <v>68</v>
       </c>
@@ -4129,7 +4129,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A70" s="5">
         <v>69</v>
       </c>
@@ -4148,7 +4148,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A71" s="5">
         <v>70</v>
       </c>
@@ -4167,7 +4167,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A72" s="5">
         <v>71</v>
       </c>
@@ -4186,7 +4186,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A73" s="5">
         <v>72</v>
       </c>
@@ -4205,7 +4205,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A74" s="5">
         <v>73</v>
       </c>
@@ -4224,7 +4224,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A75" s="5">
         <v>74</v>
       </c>
@@ -4243,7 +4243,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A76" s="5">
         <v>75</v>
       </c>
@@ -4262,7 +4262,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A77" s="5">
         <v>76</v>
       </c>
@@ -4281,7 +4281,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A78" s="5">
         <v>77</v>
       </c>
@@ -4300,7 +4300,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A79" s="5">
         <v>78</v>
       </c>
@@ -4319,7 +4319,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A80" s="5">
         <v>79</v>
       </c>
@@ -4338,7 +4338,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A81" s="5">
         <v>80</v>
       </c>
@@ -4357,7 +4357,7 @@
         <v>1435</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A82" s="5">
         <v>81</v>
       </c>
@@ -4376,7 +4376,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A83" s="5">
         <v>82</v>
       </c>
@@ -4395,7 +4395,7 @@
         <v>1710</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A84" s="5">
         <v>83</v>
       </c>
@@ -4414,7 +4414,7 @@
         <v>1910</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A85" s="5">
         <v>84</v>
       </c>
@@ -4433,7 +4433,7 @@
         <v>1922</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A86" s="5">
         <v>85</v>
       </c>
@@ -4452,7 +4452,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A87" s="5">
         <v>86</v>
       </c>
@@ -4471,7 +4471,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A88" s="5">
         <v>87</v>
       </c>
@@ -4490,7 +4490,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A89" s="5">
         <v>88</v>
       </c>
@@ -4509,7 +4509,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A90" s="5">
         <v>89</v>
       </c>
@@ -4528,7 +4528,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A91" s="5">
         <v>90</v>
       </c>
@@ -4547,7 +4547,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A92" s="5">
         <v>91</v>
       </c>
@@ -4566,7 +4566,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A93" s="5">
         <v>92</v>
       </c>
@@ -4585,7 +4585,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A94" s="5">
         <v>93</v>
       </c>
@@ -4604,7 +4604,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A95" s="5">
         <v>94</v>
       </c>
@@ -4623,7 +4623,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A96" s="5">
         <v>95</v>
       </c>
@@ -4642,7 +4642,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A97" s="5">
         <v>96</v>
       </c>
@@ -4661,7 +4661,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A98" s="5">
         <v>97</v>
       </c>
@@ -4680,7 +4680,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A99" s="5">
         <v>98</v>
       </c>
@@ -4699,7 +4699,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A100" s="5">
         <v>99</v>
       </c>
@@ -4718,7 +4718,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A101" s="5">
         <v>100</v>
       </c>
@@ -4737,7 +4737,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A102" s="5">
         <v>101</v>
       </c>
@@ -4756,7 +4756,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A103" s="5">
         <v>102</v>
       </c>
@@ -4775,7 +4775,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A104" s="5">
         <v>103</v>
       </c>
@@ -4794,7 +4794,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A105" s="5">
         <v>104</v>
       </c>
@@ -4813,7 +4813,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A106" s="5">
         <v>105</v>
       </c>
@@ -4832,7 +4832,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A107" s="5">
         <v>106</v>
       </c>
@@ -4851,7 +4851,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A108" s="5">
         <v>107</v>
       </c>
@@ -4870,7 +4870,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A109" s="5">
         <v>108</v>
       </c>
@@ -4889,7 +4889,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A110" s="5">
         <v>109</v>
       </c>
@@ -4908,7 +4908,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A111" s="5">
         <v>110</v>
       </c>
@@ -4927,7 +4927,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A112" s="5">
         <v>111</v>
       </c>
@@ -4946,7 +4946,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A113" s="5">
         <v>112</v>
       </c>
@@ -4965,7 +4965,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A114" s="5">
         <v>113</v>
       </c>
@@ -4984,7 +4984,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A115" s="5">
         <v>114</v>
       </c>
@@ -5003,7 +5003,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A116" s="5">
         <v>115</v>
       </c>
@@ -5022,7 +5022,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A117" s="5">
         <v>116</v>
       </c>
@@ -5041,7 +5041,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A118" s="5">
         <v>117</v>
       </c>
@@ -5060,7 +5060,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A119" s="5">
         <v>118</v>
       </c>
@@ -5079,7 +5079,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A120" s="5">
         <v>119</v>
       </c>
@@ -5098,7 +5098,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A121" s="5">
         <v>120</v>
       </c>
@@ -5117,7 +5117,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A122" s="5">
         <v>121</v>
       </c>
@@ -5136,7 +5136,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A123" s="5">
         <v>122</v>
       </c>
@@ -5155,7 +5155,7 @@
         <v>1273</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A124" s="5">
         <v>123</v>
       </c>
@@ -5174,7 +5174,7 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A125" s="5">
         <v>124</v>
       </c>
@@ -5193,7 +5193,7 @@
         <v>1378</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A126" s="5">
         <v>125</v>
       </c>
@@ -5212,7 +5212,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A127" s="5">
         <v>126</v>
       </c>
@@ -5231,7 +5231,7 @@
         <v>1408</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A128" s="5">
         <v>127</v>
       </c>
@@ -5250,7 +5250,7 @@
         <v>1424</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A129" s="5">
         <v>128</v>
       </c>
@@ -5269,7 +5269,7 @@
         <v>1539</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A130" s="5">
         <v>129</v>
       </c>
@@ -5288,7 +5288,7 @@
         <v>1524</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A131" s="5">
         <v>130</v>
       </c>
@@ -5307,7 +5307,7 @@
         <v>1639</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A132" s="5">
         <v>131</v>
       </c>
@@ -5326,7 +5326,7 @@
         <v>1594</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A133" s="5">
         <v>132</v>
       </c>
@@ -5345,7 +5345,7 @@
         <v>1644</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A134" s="5">
         <v>133</v>
       </c>
@@ -5364,7 +5364,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A135" s="5">
         <v>134</v>
       </c>
@@ -5383,7 +5383,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A136" s="5">
         <v>135</v>
       </c>
@@ -5402,7 +5402,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A137" s="5">
         <v>136</v>
       </c>
@@ -5421,7 +5421,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A138" s="5">
         <v>137</v>
       </c>
@@ -5440,7 +5440,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A139" s="5">
         <v>138</v>
       </c>
@@ -5459,7 +5459,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A140" s="5">
         <v>139</v>
       </c>
@@ -5478,7 +5478,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A141" s="5">
         <v>140</v>
       </c>
@@ -5497,7 +5497,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A142" s="5">
         <v>141</v>
       </c>
@@ -5516,7 +5516,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A143" s="5">
         <v>142</v>
       </c>
@@ -5535,7 +5535,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A144" s="5">
         <v>143</v>
       </c>
@@ -5554,7 +5554,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A145" s="5">
         <v>144</v>
       </c>
@@ -5573,7 +5573,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A146" s="5">
         <v>145</v>
       </c>
@@ -5592,7 +5592,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A147" s="5">
         <v>146</v>
       </c>
@@ -5611,7 +5611,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A148" s="5">
         <v>147</v>
       </c>
@@ -5630,7 +5630,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A149" s="5">
         <v>148</v>
       </c>
@@ -5649,7 +5649,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A150" s="5">
         <v>149</v>
       </c>
@@ -5668,7 +5668,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A151" s="5">
         <v>150</v>
       </c>
@@ -5687,7 +5687,7 @@
         <v>1297</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A152" s="5">
         <v>151</v>
       </c>
@@ -5706,7 +5706,7 @@
         <v>1447</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A153" s="5">
         <v>152</v>
       </c>
@@ -5725,7 +5725,7 @@
         <v>1450</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A154" s="5">
         <v>153</v>
       </c>
@@ -5744,7 +5744,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A155" s="5">
         <v>154</v>
       </c>
@@ -5763,7 +5763,7 @@
         <v>1543</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A156" s="5">
         <v>155</v>
       </c>
@@ -5782,7 +5782,7 @@
         <v>1573</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A157" s="5">
         <v>156</v>
       </c>
@@ -5801,7 +5801,7 @@
         <v>1638</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A158" s="5">
         <v>157</v>
       </c>
@@ -5820,7 +5820,7 @@
         <v>1623</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A159" s="5">
         <v>158</v>
       </c>
@@ -5839,7 +5839,7 @@
         <v>1692</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A160" s="5">
         <v>159</v>
       </c>
@@ -5858,7 +5858,7 @@
         <v>1653</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A161" s="5">
         <v>160</v>
       </c>
@@ -5877,7 +5877,7 @@
         <v>1683</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A162" s="5">
         <v>161</v>
       </c>
@@ -5896,7 +5896,7 @@
         <v>1733</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A163" s="5">
         <v>162</v>
       </c>
@@ -5915,7 +5915,7 @@
         <v>1783</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A164" s="5">
         <v>163</v>
       </c>
@@ -5934,7 +5934,7 @@
         <v>1833</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A165" s="5">
         <v>164</v>
       </c>
@@ -5953,7 +5953,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A166" s="5">
         <v>165</v>
       </c>
@@ -5972,7 +5972,7 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A167" s="5">
         <v>166</v>
       </c>
@@ -6000,18 +6000,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F171"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="7.3828125" customWidth="1"/>
-    <col min="2" max="2" width="22.765625" customWidth="1"/>
-    <col min="3" max="3" width="17.07421875" customWidth="1"/>
-    <col min="4" max="4" width="16.07421875" customWidth="1"/>
-    <col min="5" max="5" width="18.15234375" customWidth="1"/>
-    <col min="6" max="6" width="16.69140625" customWidth="1"/>
-    <col min="7" max="7" width="16.15234375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.4140625" customWidth="1"/>
+    <col min="2" max="2" width="22.75" customWidth="1"/>
+    <col min="3" max="3" width="17.08203125" customWidth="1"/>
+    <col min="4" max="4" width="16.08203125" customWidth="1"/>
+    <col min="5" max="5" width="18.1640625" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" customWidth="1"/>
+    <col min="7" max="7" width="16.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -6031,7 +6031,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -6050,7 +6050,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -6069,7 +6069,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -6088,7 +6088,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -6107,7 +6107,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -6126,7 +6126,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -6145,7 +6145,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -6164,7 +6164,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -6183,7 +6183,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -6202,7 +6202,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -6221,7 +6221,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A12" s="5">
         <v>11</v>
       </c>
@@ -6240,7 +6240,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A13" s="5">
         <v>12</v>
       </c>
@@ -6259,7 +6259,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A14" s="5">
         <v>13</v>
       </c>
@@ -6278,7 +6278,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15" s="5">
         <v>14</v>
       </c>
@@ -6297,7 +6297,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16" s="5">
         <v>15</v>
       </c>
@@ -6316,7 +6316,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17" s="5">
         <v>16</v>
       </c>
@@ -6335,7 +6335,7 @@
         <v>1274</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A18" s="5">
         <v>17</v>
       </c>
@@ -6354,7 +6354,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A19" s="5">
         <v>18</v>
       </c>
@@ -6373,7 +6373,7 @@
         <v>1413</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A20" s="5">
         <v>19</v>
       </c>
@@ -6392,7 +6392,7 @@
         <v>1497</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A21" s="5">
         <v>20</v>
       </c>
@@ -6411,7 +6411,7 @@
         <v>1529</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A22" s="5">
         <v>21</v>
       </c>
@@ -6430,7 +6430,7 @@
         <v>1579</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A23" s="5">
         <v>22</v>
       </c>
@@ -6449,7 +6449,7 @@
         <v>1707</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A24" s="5">
         <v>23</v>
       </c>
@@ -6466,7 +6466,7 @@
         <v>1707</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A25" s="5">
         <v>24</v>
       </c>
@@ -6485,7 +6485,7 @@
         <v>1759</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A26" s="5">
         <v>25</v>
       </c>
@@ -6504,7 +6504,7 @@
         <v>1804</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A27" s="5">
         <v>26</v>
       </c>
@@ -6523,7 +6523,7 @@
         <v>1842</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A28" s="5">
         <v>27</v>
       </c>
@@ -6542,7 +6542,7 @@
         <v>1885</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A29" s="5">
         <v>28</v>
       </c>
@@ -6561,7 +6561,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A30" s="5">
         <v>29</v>
       </c>
@@ -6580,7 +6580,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31" s="5">
         <v>30</v>
       </c>
@@ -6599,7 +6599,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A32" s="5">
         <v>31</v>
       </c>
@@ -6618,7 +6618,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A33" s="5">
         <v>32</v>
       </c>
@@ -6637,7 +6637,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A34" s="5">
         <v>33</v>
       </c>
@@ -6656,7 +6656,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A35" s="5">
         <v>34</v>
       </c>
@@ -6675,7 +6675,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A36" s="5">
         <v>35</v>
       </c>
@@ -6694,7 +6694,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A37" s="5">
         <v>36</v>
       </c>
@@ -6713,7 +6713,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A38" s="5">
         <v>37</v>
       </c>
@@ -6732,7 +6732,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A39" s="5">
         <v>38</v>
       </c>
@@ -6751,7 +6751,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A40" s="5">
         <v>39</v>
       </c>
@@ -6770,7 +6770,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A41" s="5">
         <v>40</v>
       </c>
@@ -6789,7 +6789,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A42" s="5">
         <v>41</v>
       </c>
@@ -6808,7 +6808,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A43" s="5">
         <v>42</v>
       </c>
@@ -6827,7 +6827,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A44" s="5">
         <v>43</v>
       </c>
@@ -6846,7 +6846,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A45" s="5">
         <v>44</v>
       </c>
@@ -6865,7 +6865,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A46" s="5">
         <v>45</v>
       </c>
@@ -6884,7 +6884,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A47" s="5">
         <v>46</v>
       </c>
@@ -6903,7 +6903,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A48" s="5">
         <v>47</v>
       </c>
@@ -6922,7 +6922,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A49" s="5">
         <v>48</v>
       </c>
@@ -6941,7 +6941,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A50" s="5">
         <v>49</v>
       </c>
@@ -6960,7 +6960,7 @@
         <v>1407</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A51" s="5">
         <v>50</v>
       </c>
@@ -6979,7 +6979,7 @@
         <v>1437</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A52" s="5">
         <v>51</v>
       </c>
@@ -6998,7 +6998,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A53" s="5">
         <v>52</v>
       </c>
@@ -7017,7 +7017,7 @@
         <v>1491</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A54" s="5">
         <v>53</v>
       </c>
@@ -7036,7 +7036,7 @@
         <v>1514</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A55" s="5">
         <v>54</v>
       </c>
@@ -7055,7 +7055,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A56" s="5">
         <v>55</v>
       </c>
@@ -7074,7 +7074,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A57" s="5">
         <v>56</v>
       </c>
@@ -7093,7 +7093,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A58" s="5">
         <v>57</v>
       </c>
@@ -7112,7 +7112,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A59" s="5">
         <v>58</v>
       </c>
@@ -7131,7 +7131,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A60" s="5">
         <v>59</v>
       </c>
@@ -7150,7 +7150,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A61" s="5">
         <v>60</v>
       </c>
@@ -7169,7 +7169,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A62" s="5">
         <v>61</v>
       </c>
@@ -7188,7 +7188,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A63" s="5">
         <v>62</v>
       </c>
@@ -7207,7 +7207,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A64" s="5">
         <v>63</v>
       </c>
@@ -7226,7 +7226,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A65" s="5">
         <v>64</v>
       </c>
@@ -7245,7 +7245,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A66" s="5">
         <v>65</v>
       </c>
@@ -7264,7 +7264,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A67" s="5">
         <v>66</v>
       </c>
@@ -7283,7 +7283,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A68" s="5">
         <v>67</v>
       </c>
@@ -7302,7 +7302,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A69" s="5">
         <v>68</v>
       </c>
@@ -7321,7 +7321,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A70" s="5">
         <v>69</v>
       </c>
@@ -7340,7 +7340,7 @@
         <v>1123</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A71" s="5">
         <v>70</v>
       </c>
@@ -7359,7 +7359,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A72" s="5">
         <v>71</v>
       </c>
@@ -7378,7 +7378,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A73" s="5">
         <v>72</v>
       </c>
@@ -7397,7 +7397,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A74" s="5">
         <v>73</v>
       </c>
@@ -7416,7 +7416,7 @@
         <v>1290</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A75" s="5">
         <v>74</v>
       </c>
@@ -7435,7 +7435,7 @@
         <v>1312</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A76" s="5">
         <v>75</v>
       </c>
@@ -7452,7 +7452,7 @@
         <v>1296</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A77" s="5">
         <v>76</v>
       </c>
@@ -7471,7 +7471,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A78" s="5">
         <v>77</v>
       </c>
@@ -7490,7 +7490,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A79" s="5">
         <v>78</v>
       </c>
@@ -7509,7 +7509,7 @@
         <v>1396</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A80" s="5">
         <v>79</v>
       </c>
@@ -7528,7 +7528,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A81" s="5">
         <v>80</v>
       </c>
@@ -7547,7 +7547,7 @@
         <v>1423</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A82" s="5">
         <v>81</v>
       </c>
@@ -7566,7 +7566,7 @@
         <v>1390</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A83" s="5">
         <v>82</v>
       </c>
@@ -7585,7 +7585,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A84" s="5">
         <v>83</v>
       </c>
@@ -7604,7 +7604,7 @@
         <v>1460</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A85" s="5">
         <v>84</v>
       </c>
@@ -7623,7 +7623,7 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A86" s="5">
         <v>85</v>
       </c>
@@ -7642,7 +7642,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A87" s="5">
         <v>86</v>
       </c>
@@ -7661,7 +7661,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A88" s="5">
         <v>87</v>
       </c>
@@ -7680,7 +7680,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A89" s="5">
         <v>88</v>
       </c>
@@ -7699,7 +7699,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A90" s="5">
         <v>89</v>
       </c>
@@ -7718,7 +7718,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A91" s="5">
         <v>90</v>
       </c>
@@ -7737,7 +7737,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A92" s="5">
         <v>91</v>
       </c>
@@ -7756,7 +7756,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A93" s="5">
         <v>92</v>
       </c>
@@ -7775,7 +7775,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A94" s="5">
         <v>93</v>
       </c>
@@ -7794,7 +7794,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A95" s="5">
         <v>94</v>
       </c>
@@ -7813,7 +7813,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A96" s="5">
         <v>95</v>
       </c>
@@ -7832,7 +7832,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A97" s="5">
         <v>96</v>
       </c>
@@ -7851,7 +7851,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A98" s="5">
         <v>97</v>
       </c>
@@ -7870,7 +7870,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A99" s="5">
         <v>98</v>
       </c>
@@ -7889,7 +7889,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A100" s="5">
         <v>99</v>
       </c>
@@ -7908,7 +7908,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A101" s="5">
         <v>100</v>
       </c>
@@ -7927,7 +7927,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A102" s="5">
         <v>101</v>
       </c>
@@ -7946,7 +7946,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A103" s="5">
         <v>102</v>
       </c>
@@ -7965,7 +7965,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A104" s="5">
         <v>103</v>
       </c>
@@ -7984,7 +7984,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A105" s="5">
         <v>104</v>
       </c>
@@ -8003,7 +8003,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A106" s="5">
         <v>105</v>
       </c>
@@ -8022,7 +8022,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A107" s="5">
         <v>106</v>
       </c>
@@ -8041,7 +8041,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A108" s="5">
         <v>107</v>
       </c>
@@ -8060,7 +8060,7 @@
         <v>1337</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A109" s="5">
         <v>108</v>
       </c>
@@ -8079,7 +8079,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A110" s="5">
         <v>109</v>
       </c>
@@ -8098,7 +8098,7 @@
         <v>1417</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A111" s="5">
         <v>110</v>
       </c>
@@ -8117,7 +8117,7 @@
         <v>1517</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A112" s="5">
         <v>111</v>
       </c>
@@ -8136,7 +8136,7 @@
         <v>1720</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A113" s="5">
         <v>112</v>
       </c>
@@ -8155,7 +8155,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A114" s="5">
         <v>113</v>
       </c>
@@ -8174,7 +8174,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A115" s="5">
         <v>114</v>
       </c>
@@ -8193,7 +8193,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A116" s="5">
         <v>115</v>
       </c>
@@ -8212,7 +8212,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A117" s="5">
         <v>116</v>
       </c>
@@ -8231,7 +8231,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A118" s="5">
         <v>117</v>
       </c>
@@ -8250,7 +8250,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A119" s="5">
         <v>118</v>
       </c>
@@ -8269,7 +8269,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A120" s="5">
         <v>119</v>
       </c>
@@ -8288,7 +8288,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A121" s="5">
         <v>120</v>
       </c>
@@ -8307,7 +8307,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A122" s="5">
         <v>121</v>
       </c>
@@ -8326,7 +8326,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A123" s="5">
         <v>122</v>
       </c>
@@ -8345,7 +8345,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A124" s="5">
         <v>123</v>
       </c>
@@ -8364,7 +8364,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A125" s="5">
         <v>124</v>
       </c>
@@ -8383,7 +8383,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A126" s="5">
         <v>125</v>
       </c>
@@ -8402,7 +8402,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A127" s="5">
         <v>126</v>
       </c>
@@ -8421,7 +8421,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A128" s="5">
         <v>127</v>
       </c>
@@ -8440,7 +8440,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A129" s="5">
         <v>128</v>
       </c>
@@ -8459,7 +8459,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A130" s="5">
         <v>129</v>
       </c>
@@ -8478,7 +8478,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A131" s="5">
         <v>130</v>
       </c>
@@ -8497,7 +8497,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A132" s="5">
         <v>131</v>
       </c>
@@ -8516,7 +8516,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A133" s="5">
         <v>132</v>
       </c>
@@ -8535,7 +8535,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A134" s="5">
         <v>133</v>
       </c>
@@ -8554,7 +8554,7 @@
         <v>1422</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A135" s="5">
         <v>134</v>
       </c>
@@ -8573,7 +8573,7 @@
         <v>1409</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A136" s="5">
         <v>135</v>
       </c>
@@ -8592,7 +8592,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A137" s="5">
         <v>136</v>
       </c>
@@ -8611,7 +8611,7 @@
         <v>1628.5</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A138" s="5">
         <v>137</v>
       </c>
@@ -8630,7 +8630,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A139" s="5">
         <v>138</v>
       </c>
@@ -8649,7 +8649,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A140" s="5">
         <v>139</v>
       </c>
@@ -8668,7 +8668,7 @@
         <v>1869</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A141" s="5">
         <v>140</v>
       </c>
@@ -8687,7 +8687,7 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A142" s="5">
         <v>141</v>
       </c>
@@ -8706,7 +8706,7 @@
         <v>1959</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A143" s="5">
         <v>142</v>
       </c>
@@ -8725,7 +8725,7 @@
         <v>2059</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A144" s="5">
         <v>143</v>
       </c>
@@ -8744,7 +8744,7 @@
         <v>2089</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A145" s="5">
         <v>144</v>
       </c>
@@ -8763,7 +8763,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A146" s="5">
         <v>145</v>
       </c>
@@ -8782,7 +8782,7 @@
         <v>2209</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A147" s="5">
         <v>146</v>
       </c>
@@ -8801,7 +8801,7 @@
         <v>2289</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A148" s="5">
         <v>147</v>
       </c>
@@ -8820,7 +8820,7 @@
         <v>2349</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A149" s="5">
         <v>148</v>
       </c>
@@ -8839,7 +8839,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A150" s="5">
         <v>149</v>
       </c>
@@ -8858,7 +8858,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A151" s="5">
         <v>150</v>
       </c>
@@ -8877,7 +8877,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A152" s="5">
         <v>151</v>
       </c>
@@ -8896,7 +8896,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A153" s="5">
         <v>152</v>
       </c>
@@ -8915,7 +8915,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A154" s="5">
         <v>153</v>
       </c>
@@ -8934,7 +8934,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A155" s="5">
         <v>154</v>
       </c>
@@ -8953,7 +8953,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A156" s="5">
         <v>155</v>
       </c>
@@ -8972,7 +8972,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A157" s="5">
         <v>156</v>
       </c>
@@ -8991,7 +8991,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A158" s="5">
         <v>157</v>
       </c>
@@ -9010,7 +9010,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A159" s="5">
         <v>158</v>
       </c>
@@ -9029,7 +9029,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A160" s="5">
         <v>159</v>
       </c>
@@ -9048,7 +9048,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A161" s="5">
         <v>160</v>
       </c>
@@ -9067,7 +9067,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A162" s="5">
         <v>161</v>
       </c>
@@ -9086,7 +9086,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A163" s="5">
         <v>162</v>
       </c>
@@ -9105,7 +9105,7 @@
         <v>1306</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A164" s="5">
         <v>163</v>
       </c>
@@ -9124,7 +9124,7 @@
         <v>1248</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A165" s="5">
         <v>164</v>
       </c>
@@ -9143,7 +9143,7 @@
         <v>1398</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A166" s="5">
         <v>165</v>
       </c>
@@ -9162,7 +9162,7 @@
         <v>1461</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A167" s="5">
         <v>166</v>
       </c>
@@ -9181,7 +9181,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A168" s="5">
         <v>167</v>
       </c>
@@ -9200,7 +9200,7 @@
         <v>1711</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A169" s="5">
         <v>168</v>
       </c>
@@ -9219,7 +9219,7 @@
         <v>1811</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A170" s="5">
         <v>169</v>
       </c>
@@ -9238,7 +9238,7 @@
         <v>1841</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A171" s="5">
         <v>170</v>
       </c>
@@ -9267,16 +9267,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F156"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="18.61328125" customWidth="1"/>
-    <col min="3" max="3" width="15.3828125" customWidth="1"/>
+    <col min="2" max="2" width="18.58203125" customWidth="1"/>
+    <col min="3" max="3" width="15.4140625" customWidth="1"/>
     <col min="4" max="4" width="18" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.69140625" customWidth="1"/>
-    <col min="6" max="6" width="16.4609375" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="6" max="6" width="16.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -9296,7 +9296,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -9315,7 +9315,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -9334,7 +9334,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -9353,7 +9353,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -9372,7 +9372,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -9391,7 +9391,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -9410,7 +9410,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -9429,7 +9429,7 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -9448,7 +9448,7 @@
         <v>1293</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -9467,7 +9467,7 @@
         <v>1343</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -9486,7 +9486,7 @@
         <v>1391</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A12" s="5">
         <v>11</v>
       </c>
@@ -9505,7 +9505,7 @@
         <v>1421</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A13" s="5">
         <v>12</v>
       </c>
@@ -9524,7 +9524,7 @@
         <v>1466</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A14" s="5">
         <v>13</v>
       </c>
@@ -9543,7 +9543,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15" s="5">
         <v>14</v>
       </c>
@@ -9562,7 +9562,7 @@
         <v>1524</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16" s="5">
         <v>15</v>
       </c>
@@ -9581,7 +9581,7 @@
         <v>1574</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17" s="5">
         <v>16</v>
       </c>
@@ -9600,7 +9600,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A18" s="5">
         <v>17</v>
       </c>
@@ -9619,7 +9619,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A19" s="5">
         <v>18</v>
       </c>
@@ -9638,7 +9638,7 @@
         <v>1737</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A20" s="5">
         <v>19</v>
       </c>
@@ -9657,7 +9657,7 @@
         <v>1805</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A21" s="5">
         <v>20</v>
       </c>
@@ -9676,7 +9676,7 @@
         <v>1853</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A22" s="5">
         <v>21</v>
       </c>
@@ -9695,7 +9695,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A23" s="5">
         <v>22</v>
       </c>
@@ -9714,7 +9714,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A24" s="5">
         <v>23</v>
       </c>
@@ -9733,7 +9733,7 @@
         <v>1856</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A25" s="5">
         <v>24</v>
       </c>
@@ -9752,7 +9752,7 @@
         <v>1911</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A26" s="5">
         <v>25</v>
       </c>
@@ -9771,7 +9771,7 @@
         <v>1958</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A27" s="5">
         <v>26</v>
       </c>
@@ -9790,7 +9790,7 @@
         <v>2058</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A28" s="5">
         <v>27</v>
       </c>
@@ -9809,7 +9809,7 @@
         <v>2038</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A29" s="5">
         <v>28</v>
       </c>
@@ -9828,7 +9828,7 @@
         <v>2063</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A30" s="5">
         <v>29</v>
       </c>
@@ -9847,7 +9847,7 @@
         <v>2045</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31" s="5">
         <v>30</v>
       </c>
@@ -9866,7 +9866,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A32" s="5">
         <v>31</v>
       </c>
@@ -9885,7 +9885,7 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A33" s="5">
         <v>32</v>
       </c>
@@ -9904,7 +9904,7 @@
         <v>2178</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A34" s="5">
         <v>33</v>
       </c>
@@ -9923,7 +9923,7 @@
         <v>2194</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A35" s="5">
         <v>34</v>
       </c>
@@ -9942,7 +9942,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A36" s="5">
         <v>35</v>
       </c>
@@ -9961,7 +9961,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A37" s="5">
         <v>36</v>
       </c>
@@ -9980,7 +9980,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A38" s="5">
         <v>37</v>
       </c>
@@ -9999,7 +9999,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A39" s="5">
         <v>38</v>
       </c>
@@ -10018,7 +10018,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A40" s="5">
         <v>39</v>
       </c>
@@ -10037,7 +10037,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A41" s="5">
         <v>40</v>
       </c>
@@ -10056,7 +10056,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A42" s="5">
         <v>41</v>
       </c>
@@ -10075,7 +10075,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A43" s="5">
         <v>42</v>
       </c>
@@ -10094,7 +10094,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A44" s="5">
         <v>43</v>
       </c>
@@ -10113,7 +10113,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A45" s="5">
         <v>44</v>
       </c>
@@ -10132,7 +10132,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A46" s="5">
         <v>45</v>
       </c>
@@ -10151,7 +10151,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A47" s="5">
         <v>46</v>
       </c>
@@ -10170,7 +10170,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A48" s="5">
         <v>47</v>
       </c>
@@ -10189,7 +10189,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A49" s="5">
         <v>48</v>
       </c>
@@ -10208,7 +10208,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A50" s="5">
         <v>49</v>
       </c>
@@ -10227,7 +10227,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A51" s="5">
         <v>50</v>
       </c>
@@ -10246,7 +10246,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A52" s="5">
         <v>51</v>
       </c>
@@ -10265,7 +10265,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A53" s="5">
         <v>52</v>
       </c>
@@ -10284,7 +10284,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A54" s="5">
         <v>53</v>
       </c>
@@ -10303,7 +10303,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A55" s="5">
         <v>54</v>
       </c>
@@ -10322,7 +10322,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A56" s="5">
         <v>55</v>
       </c>
@@ -10341,7 +10341,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A57" s="5">
         <v>56</v>
       </c>
@@ -10360,7 +10360,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A58" s="5">
         <v>57</v>
       </c>
@@ -10379,7 +10379,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A59" s="5">
         <v>58</v>
       </c>
@@ -10398,7 +10398,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A60" s="5">
         <v>59</v>
       </c>
@@ -10417,7 +10417,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A61" s="5">
         <v>60</v>
       </c>
@@ -10436,7 +10436,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A62" s="5">
         <v>61</v>
       </c>
@@ -10455,7 +10455,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A63" s="5">
         <v>62</v>
       </c>
@@ -10474,7 +10474,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A64" s="5">
         <v>63</v>
       </c>
@@ -10493,7 +10493,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A65" s="5">
         <v>64</v>
       </c>
@@ -10512,7 +10512,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A66" s="5">
         <v>65</v>
       </c>
@@ -10531,7 +10531,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A67" s="5">
         <v>66</v>
       </c>
@@ -10550,7 +10550,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A68" s="5">
         <v>67</v>
       </c>
@@ -10569,7 +10569,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A69" s="5">
         <v>68</v>
       </c>
@@ -10588,7 +10588,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A70" s="5">
         <v>69</v>
       </c>
@@ -10607,7 +10607,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A71" s="5">
         <v>70</v>
       </c>
@@ -10626,7 +10626,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A72" s="5">
         <v>71</v>
       </c>
@@ -10645,7 +10645,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A73" s="5">
         <v>72</v>
       </c>
@@ -10664,7 +10664,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A74" s="5">
         <v>73</v>
       </c>
@@ -10683,7 +10683,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A75" s="5">
         <v>74</v>
       </c>
@@ -10702,7 +10702,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A76" s="5">
         <v>75</v>
       </c>
@@ -10721,7 +10721,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A77" s="5">
         <v>76</v>
       </c>
@@ -10740,7 +10740,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A78" s="5">
         <v>77</v>
       </c>
@@ -10759,7 +10759,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A79" s="5">
         <v>78</v>
       </c>
@@ -10778,7 +10778,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A80" s="5">
         <v>79</v>
       </c>
@@ -10797,7 +10797,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A81" s="5">
         <v>80</v>
       </c>
@@ -10816,7 +10816,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A82" s="5">
         <v>81</v>
       </c>
@@ -10835,7 +10835,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A83" s="5">
         <v>82</v>
       </c>
@@ -10854,7 +10854,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A84" s="5">
         <v>83</v>
       </c>
@@ -10873,7 +10873,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A85" s="5">
         <v>84</v>
       </c>
@@ -10892,7 +10892,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A86" s="5">
         <v>85</v>
       </c>
@@ -10911,7 +10911,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A87" s="5">
         <v>86</v>
       </c>
@@ -10930,7 +10930,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A88" s="5">
         <v>87</v>
       </c>
@@ -10949,7 +10949,7 @@
         <v>844.5</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A89" s="5">
         <v>88</v>
       </c>
@@ -10968,7 +10968,7 @@
         <v>922.5</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A90" s="5">
         <v>89</v>
       </c>
@@ -10987,7 +10987,7 @@
         <v>952.5</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A91" s="5">
         <v>90</v>
       </c>
@@ -11006,7 +11006,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A92" s="5">
         <v>91</v>
       </c>
@@ -11025,7 +11025,7 @@
         <v>982.5</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A93" s="5">
         <v>92</v>
       </c>
@@ -11044,7 +11044,7 @@
         <v>962.5</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A94" s="5">
         <v>93</v>
       </c>
@@ -11063,7 +11063,7 @@
         <v>941.5</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A95" s="5">
         <v>94</v>
       </c>
@@ -11082,7 +11082,7 @@
         <v>991.5</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A96" s="5">
         <v>95</v>
       </c>
@@ -11101,7 +11101,7 @@
         <v>1075.5</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A97" s="5">
         <v>96</v>
       </c>
@@ -11120,7 +11120,7 @@
         <v>1080.5</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A98" s="5">
         <v>97</v>
       </c>
@@ -11139,7 +11139,7 @@
         <v>1125.5</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A99" s="5">
         <v>98</v>
       </c>
@@ -11158,7 +11158,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A100" s="5">
         <v>99</v>
       </c>
@@ -11177,7 +11177,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A101" s="5">
         <v>100</v>
       </c>
@@ -11196,7 +11196,7 @@
         <v>1261.5</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A102" s="5">
         <v>101</v>
       </c>
@@ -11215,7 +11215,7 @@
         <v>1414.5</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A103" s="5">
         <v>102</v>
       </c>
@@ -11234,7 +11234,7 @@
         <v>1459.5</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A104" s="5">
         <v>103</v>
       </c>
@@ -11253,7 +11253,7 @@
         <v>1507.5</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A105" s="5">
         <v>104</v>
       </c>
@@ -11272,7 +11272,7 @@
         <v>30.5</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A106" s="5">
         <v>105</v>
       </c>
@@ -11291,7 +11291,7 @@
         <v>63.5</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A107" s="5">
         <v>106</v>
       </c>
@@ -11310,7 +11310,7 @@
         <v>163.5</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A108" s="5">
         <v>107</v>
       </c>
@@ -11329,7 +11329,7 @@
         <v>247.5</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A109" s="5">
         <v>108</v>
       </c>
@@ -11348,7 +11348,7 @@
         <v>277.5</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A110" s="5">
         <v>109</v>
       </c>
@@ -11367,7 +11367,7 @@
         <v>465.5</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A111" s="5">
         <v>110</v>
       </c>
@@ -11386,7 +11386,7 @@
         <v>515.5</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A112" s="5">
         <v>111</v>
       </c>
@@ -11405,7 +11405,7 @@
         <v>615.5</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A113" s="5">
         <v>112</v>
       </c>
@@ -11424,7 +11424,7 @@
         <v>660.5</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A114" s="5">
         <v>113</v>
       </c>
@@ -11443,7 +11443,7 @@
         <v>690.5</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A115" s="5">
         <v>114</v>
       </c>
@@ -11462,7 +11462,7 @@
         <v>896.5</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A116" s="5">
         <v>115</v>
       </c>
@@ -11481,7 +11481,7 @@
         <v>951.5</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A117" s="5">
         <v>116</v>
       </c>
@@ -11500,7 +11500,7 @@
         <v>1001.5</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A118" s="5">
         <v>117</v>
       </c>
@@ -11519,7 +11519,7 @@
         <v>1151.5</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A119" s="5">
         <v>118</v>
       </c>
@@ -11538,7 +11538,7 @@
         <v>1154.5</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A120" s="5">
         <v>119</v>
       </c>
@@ -11557,7 +11557,7 @@
         <v>1119.5</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A121" s="5">
         <v>120</v>
       </c>
@@ -11576,7 +11576,7 @@
         <v>1149.5</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A122" s="5">
         <v>121</v>
       </c>
@@ -11595,7 +11595,7 @@
         <v>1256.5</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A123" s="5">
         <v>122</v>
       </c>
@@ -11614,7 +11614,7 @@
         <v>1317.5</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A124" s="5">
         <v>123</v>
       </c>
@@ -11633,7 +11633,7 @@
         <v>1452.5</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A125" s="5">
         <v>124</v>
       </c>
@@ -11652,7 +11652,7 @@
         <v>1569.5</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A126" s="5">
         <v>125</v>
       </c>
@@ -11671,7 +11671,7 @@
         <v>1574.5</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A127" s="5">
         <v>126</v>
       </c>
@@ -11690,7 +11690,7 @@
         <v>1589.5</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A128" s="5">
         <v>127</v>
       </c>
@@ -11709,7 +11709,7 @@
         <v>1649.5</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A129" s="5">
         <v>128</v>
       </c>
@@ -11728,7 +11728,7 @@
         <v>1709.5</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A130" s="5">
         <v>129</v>
       </c>
@@ -11747,7 +11747,7 @@
         <v>1741.5</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A131" s="5">
         <v>130</v>
       </c>
@@ -11766,7 +11766,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A132" s="5">
         <v>131</v>
       </c>
@@ -11785,7 +11785,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A133" s="5">
         <v>132</v>
       </c>
@@ -11804,7 +11804,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A134" s="5">
         <v>133</v>
       </c>
@@ -11823,7 +11823,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A135" s="5">
         <v>134</v>
       </c>
@@ -11842,7 +11842,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A136" s="5">
         <v>135</v>
       </c>
@@ -11861,7 +11861,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A137" s="5">
         <v>136</v>
       </c>
@@ -11880,7 +11880,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A138" s="5">
         <v>137</v>
       </c>
@@ -11899,7 +11899,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A139" s="5">
         <v>138</v>
       </c>
@@ -11918,7 +11918,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A140" s="5">
         <v>139</v>
       </c>
@@ -11937,7 +11937,7 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A141" s="5">
         <v>140</v>
       </c>
@@ -11956,7 +11956,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A142" s="5">
         <v>141</v>
       </c>
@@ -11975,7 +11975,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A143" s="5">
         <v>142</v>
       </c>
@@ -11994,7 +11994,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A144" s="5">
         <v>143</v>
       </c>
@@ -12013,7 +12013,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A145" s="5">
         <v>144</v>
       </c>
@@ -12032,7 +12032,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A146" s="5">
         <v>145</v>
       </c>
@@ -12051,7 +12051,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A147" s="5">
         <v>146</v>
       </c>
@@ -12070,7 +12070,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A148" s="5">
         <v>147</v>
       </c>
@@ -12089,7 +12089,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A149" s="5">
         <v>148</v>
       </c>
@@ -12108,7 +12108,7 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A150" s="5">
         <v>149</v>
       </c>
@@ -12127,7 +12127,7 @@
         <v>1816</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A151" s="5">
         <v>150</v>
       </c>
@@ -12146,7 +12146,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A152" s="5">
         <v>151</v>
       </c>
@@ -12165,7 +12165,7 @@
         <v>1966</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A153" s="5">
         <v>152</v>
       </c>
@@ -12184,7 +12184,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A154" s="5">
         <v>153</v>
       </c>
@@ -12203,7 +12203,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A155" s="5">
         <v>154</v>
       </c>
@@ -12222,7 +12222,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A156" s="5">
         <v>155</v>
       </c>
@@ -12249,22 +12249,22 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A2:B8"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="45.3046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.69140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="45.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="B2" s="22"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3" s="23" t="s">
         <v>49</v>
       </c>
       <c r="B3" s="23"/>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>50</v>
       </c>
@@ -12272,7 +12272,7 @@
         <v>47200000</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>51</v>
       </c>
@@ -12280,7 +12280,7 @@
         <v>2625000</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>52</v>
       </c>
@@ -12288,7 +12288,7 @@
         <v>21460000</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -12305,21 +12305,21 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:L149"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="13.4609375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.69140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.3828125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.69140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.07421875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.23046875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.3046875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.15234375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.69140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.15234375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.4140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.08203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A1" s="26" t="s">
         <v>48</v>
       </c>
@@ -12330,7 +12330,7 @@
       <c r="F1" s="26"/>
       <c r="G1" s="26"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -12339,7 +12339,7 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -12350,7 +12350,7 @@
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
@@ -12382,7 +12382,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A5" s="5">
         <v>1</v>
       </c>
@@ -12414,7 +12414,7 @@
         <v>7484</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A6" s="5">
         <v>2</v>
       </c>
@@ -12434,7 +12434,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A7" s="5">
         <v>3</v>
       </c>
@@ -12454,7 +12454,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A8" s="5">
         <v>4</v>
       </c>
@@ -12474,7 +12474,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A9" s="5">
         <v>5</v>
       </c>
@@ -12494,7 +12494,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A10" s="5">
         <v>6</v>
       </c>
@@ -12514,7 +12514,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A11" s="5">
         <v>7</v>
       </c>
@@ -12534,7 +12534,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A12" s="5">
         <v>8</v>
       </c>
@@ -12554,7 +12554,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A13" s="5">
         <v>9</v>
       </c>
@@ -12574,7 +12574,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A14" s="5">
         <v>10</v>
       </c>
@@ -12594,7 +12594,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A15" s="5">
         <v>11</v>
       </c>
@@ -12614,7 +12614,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A16" s="5">
         <v>12</v>
       </c>
@@ -12634,7 +12634,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A17" s="5">
         <v>13</v>
       </c>
@@ -12654,7 +12654,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A18" s="5">
         <v>14</v>
       </c>
@@ -12674,7 +12674,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A19" s="5">
         <v>15</v>
       </c>
@@ -12694,7 +12694,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A20" s="5">
         <v>16</v>
       </c>
@@ -12714,7 +12714,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A21" s="5">
         <v>17</v>
       </c>
@@ -12734,7 +12734,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A22" s="5">
         <v>18</v>
       </c>
@@ -12754,7 +12754,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A23" s="5">
         <v>19</v>
       </c>
@@ -12774,7 +12774,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A24" s="5">
         <v>20</v>
       </c>
@@ -12794,7 +12794,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A25" s="5">
         <v>21</v>
       </c>
@@ -12814,7 +12814,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A26" s="5">
         <v>22</v>
       </c>
@@ -12834,7 +12834,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A27" s="5">
         <v>23</v>
       </c>
@@ -12854,7 +12854,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A28" s="5">
         <v>24</v>
       </c>
@@ -12874,7 +12874,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A29" s="5">
         <v>25</v>
       </c>
@@ -12894,7 +12894,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A30" s="5">
         <v>26</v>
       </c>
@@ -12914,7 +12914,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A31" s="5">
         <v>27</v>
       </c>
@@ -12934,7 +12934,7 @@
         <v>1329</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A32" s="5">
         <v>28</v>
       </c>
@@ -12954,7 +12954,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A33" s="5">
         <v>29</v>
       </c>
@@ -12974,7 +12974,7 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A34" s="5">
         <v>30</v>
       </c>
@@ -12994,7 +12994,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A35" s="5">
         <v>31</v>
       </c>
@@ -13014,7 +13014,7 @@
         <v>1555</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A36" s="5">
         <v>32</v>
       </c>
@@ -13034,7 +13034,7 @@
         <v>1627</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A37" s="5">
         <v>33</v>
       </c>
@@ -13054,7 +13054,7 @@
         <v>1663</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A38" s="5">
         <v>34</v>
       </c>
@@ -13074,7 +13074,7 @@
         <v>1708</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A39" s="5">
         <v>35</v>
       </c>
@@ -13094,7 +13094,7 @@
         <v>1790</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A40" s="5">
         <v>36</v>
       </c>
@@ -13114,7 +13114,7 @@
         <v>1844</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A41" s="5">
         <v>37</v>
       </c>
@@ -13134,7 +13134,7 @@
         <v>1871</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A42" s="5">
         <v>38</v>
       </c>
@@ -13154,7 +13154,7 @@
         <v>1907</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A43" s="5">
         <v>39</v>
       </c>
@@ -13174,7 +13174,7 @@
         <v>1952</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A44" s="5">
         <v>40</v>
       </c>
@@ -13194,7 +13194,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A45" s="5">
         <v>41</v>
       </c>
@@ -13214,7 +13214,7 @@
         <v>2073</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A46" s="5">
         <v>42</v>
       </c>
@@ -13234,7 +13234,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A47" s="5">
         <v>43</v>
       </c>
@@ -13254,7 +13254,7 @@
         <v>2171</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A48" s="5">
         <v>44</v>
       </c>
@@ -13274,7 +13274,7 @@
         <v>2207</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A49" s="5">
         <v>45</v>
       </c>
@@ -13294,7 +13294,7 @@
         <v>2242</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A50" s="5">
         <v>46</v>
       </c>
@@ -13314,7 +13314,7 @@
         <v>2305</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A51" s="5">
         <v>47</v>
       </c>
@@ -13334,7 +13334,7 @@
         <v>2392</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A52" s="5">
         <v>48</v>
       </c>
@@ -13354,7 +13354,7 @@
         <v>2435</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A53" s="5">
         <v>49</v>
       </c>
@@ -13374,7 +13374,7 @@
         <v>2440</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A54" s="5">
         <v>50</v>
       </c>
@@ -13394,7 +13394,7 @@
         <v>2493</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A55" s="5">
         <v>51</v>
       </c>
@@ -13414,7 +13414,7 @@
         <v>2540</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A56" s="5">
         <v>52</v>
       </c>
@@ -13434,7 +13434,7 @@
         <v>2576</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A57" s="5">
         <v>53</v>
       </c>
@@ -13454,7 +13454,7 @@
         <v>2612</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A58" s="5">
         <v>54</v>
       </c>
@@ -13474,7 +13474,7 @@
         <v>2711</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A59" s="5">
         <v>55</v>
       </c>
@@ -13494,7 +13494,7 @@
         <v>2756</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A60" s="5">
         <v>56</v>
       </c>
@@ -13514,7 +13514,7 @@
         <v>2761</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A61" s="5">
         <v>57</v>
       </c>
@@ -13534,7 +13534,7 @@
         <v>2811</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A62" s="5">
         <v>58</v>
       </c>
@@ -13554,7 +13554,7 @@
         <v>2859</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A63" s="5">
         <v>59</v>
       </c>
@@ -13574,7 +13574,7 @@
         <v>2904</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A64" s="5">
         <v>60</v>
       </c>
@@ -13594,7 +13594,7 @@
         <v>2956</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A65" s="5">
         <v>61</v>
       </c>
@@ -13614,7 +13614,7 @@
         <v>3059</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A66" s="5">
         <v>62</v>
       </c>
@@ -13634,7 +13634,7 @@
         <v>3176</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A67" s="5">
         <v>63</v>
       </c>
@@ -13654,7 +13654,7 @@
         <v>3287</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A68" s="5">
         <v>64</v>
       </c>
@@ -13674,7 +13674,7 @@
         <v>3359</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A69" s="5">
         <v>65</v>
       </c>
@@ -13694,7 +13694,7 @@
         <v>3434</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A70" s="5">
         <v>66</v>
       </c>
@@ -13714,7 +13714,7 @@
         <v>3439</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A71" s="5">
         <v>67</v>
       </c>
@@ -13734,7 +13734,7 @@
         <v>3444</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A72" s="5">
         <v>68</v>
       </c>
@@ -13754,7 +13754,7 @@
         <v>3459</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A73" s="5">
         <v>69</v>
       </c>
@@ -13774,7 +13774,7 @@
         <v>3498</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A74" s="5">
         <v>70</v>
       </c>
@@ -13794,7 +13794,7 @@
         <v>3503</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A75" s="5">
         <v>71</v>
       </c>
@@ -13814,7 +13814,7 @@
         <v>3540</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A78" s="3" t="s">
         <v>0</v>
       </c>
@@ -13837,7 +13837,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A79" s="5">
         <v>1</v>
       </c>
@@ -13857,7 +13857,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A80" s="5">
         <v>2</v>
       </c>
@@ -13877,7 +13877,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A81" s="5">
         <v>3</v>
       </c>
@@ -13897,7 +13897,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A82" s="5">
         <v>4</v>
       </c>
@@ -13917,7 +13917,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A83" s="5">
         <v>5</v>
       </c>
@@ -13937,7 +13937,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A84" s="5">
         <v>6</v>
       </c>
@@ -13957,7 +13957,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A85" s="5">
         <v>7</v>
       </c>
@@ -13977,7 +13977,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A86" s="5">
         <v>8</v>
       </c>
@@ -13997,7 +13997,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A87" s="5">
         <v>9</v>
       </c>
@@ -14017,7 +14017,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A88" s="5">
         <v>10</v>
       </c>
@@ -14037,7 +14037,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A89" s="5">
         <v>11</v>
       </c>
@@ -14057,7 +14057,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A90" s="5">
         <v>12</v>
       </c>
@@ -14077,7 +14077,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A91" s="5">
         <v>13</v>
       </c>
@@ -14097,7 +14097,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A92" s="5">
         <v>14</v>
       </c>
@@ -14117,7 +14117,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A93" s="5">
         <v>15</v>
       </c>
@@ -14137,7 +14137,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A94" s="5">
         <v>16</v>
       </c>
@@ -14157,7 +14157,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A95" s="5">
         <v>17</v>
       </c>
@@ -14177,7 +14177,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A96" s="5">
         <v>18</v>
       </c>
@@ -14197,7 +14197,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A97" s="5">
         <v>19</v>
       </c>
@@ -14217,7 +14217,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A98" s="5">
         <v>20</v>
       </c>
@@ -14237,7 +14237,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A99" s="5">
         <v>21</v>
       </c>
@@ -14257,7 +14257,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A100" s="5">
         <v>22</v>
       </c>
@@ -14277,7 +14277,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A101" s="5">
         <v>23</v>
       </c>
@@ -14297,7 +14297,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A102" s="5">
         <v>24</v>
       </c>
@@ -14317,7 +14317,7 @@
         <v>1272</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A103" s="5">
         <v>25</v>
       </c>
@@ -14337,7 +14337,7 @@
         <v>1342</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A104" s="5">
         <v>26</v>
       </c>
@@ -14357,7 +14357,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A105" s="5">
         <v>27</v>
       </c>
@@ -14377,7 +14377,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A106" s="5">
         <v>28</v>
       </c>
@@ -14397,7 +14397,7 @@
         <v>1497</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A107" s="5">
         <v>29</v>
       </c>
@@ -14417,7 +14417,7 @@
         <v>1541</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A108" s="5">
         <v>30</v>
       </c>
@@ -14437,7 +14437,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A109" s="5">
         <v>31</v>
       </c>
@@ -14457,7 +14457,7 @@
         <v>1588</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A110" s="5">
         <v>32</v>
       </c>
@@ -14477,7 +14477,7 @@
         <v>1648</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A111" s="5">
         <v>33</v>
       </c>
@@ -14497,7 +14497,7 @@
         <v>1719</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A112" s="5">
         <v>34</v>
       </c>
@@ -14517,7 +14517,7 @@
         <v>1771</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A113" s="5">
         <v>35</v>
       </c>
@@ -14537,7 +14537,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A114" s="5">
         <v>36</v>
       </c>
@@ -14557,7 +14557,7 @@
         <v>1895</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A115" s="5">
         <v>37</v>
       </c>
@@ -14577,7 +14577,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A116" s="5">
         <v>38</v>
       </c>
@@ -14597,7 +14597,7 @@
         <v>1980</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A117" s="5">
         <v>39</v>
       </c>
@@ -14617,7 +14617,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A118" s="5">
         <v>40</v>
       </c>
@@ -14637,7 +14637,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A119" s="5">
         <v>41</v>
       </c>
@@ -14657,7 +14657,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A120" s="5">
         <v>42</v>
       </c>
@@ -14677,7 +14677,7 @@
         <v>2234</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A121" s="5">
         <v>43</v>
       </c>
@@ -14697,7 +14697,7 @@
         <v>2314</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A122" s="5">
         <v>44</v>
       </c>
@@ -14717,7 +14717,7 @@
         <v>2402</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A123" s="5">
         <v>45</v>
       </c>
@@ -14737,7 +14737,7 @@
         <v>2530</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A124" s="5">
         <v>46</v>
       </c>
@@ -14757,7 +14757,7 @@
         <v>2556</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A125" s="5">
         <v>47</v>
       </c>
@@ -14777,7 +14777,7 @@
         <v>2627</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A126" s="5">
         <v>48</v>
       </c>
@@ -14797,7 +14797,7 @@
         <v>2694</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A127" s="5">
         <v>49</v>
       </c>
@@ -14817,7 +14817,7 @@
         <v>2826</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A128" s="5">
         <v>50</v>
       </c>
@@ -14837,7 +14837,7 @@
         <v>2861</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A129" s="5">
         <v>51</v>
       </c>
@@ -14857,7 +14857,7 @@
         <v>2922</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A130" s="5">
         <v>52</v>
       </c>
@@ -14877,7 +14877,7 @@
         <v>3005</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A131" s="5">
         <v>53</v>
       </c>
@@ -14897,7 +14897,7 @@
         <v>3083</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A132" s="5">
         <v>54</v>
       </c>
@@ -14917,7 +14917,7 @@
         <v>3128</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A133" s="5">
         <v>55</v>
       </c>
@@ -14937,7 +14937,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A134" s="5">
         <v>56</v>
       </c>
@@ -14957,7 +14957,7 @@
         <v>3243</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A135" s="5">
         <v>57</v>
       </c>
@@ -14977,7 +14977,7 @@
         <v>3315</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A136" s="5">
         <v>58</v>
       </c>
@@ -14997,7 +14997,7 @@
         <v>3396</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A137" s="5">
         <v>59</v>
       </c>
@@ -15017,7 +15017,7 @@
         <v>3483</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A138" s="5">
         <v>60</v>
       </c>
@@ -15037,7 +15037,7 @@
         <v>3535</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A139" s="5">
         <v>61</v>
       </c>
@@ -15057,7 +15057,7 @@
         <v>3588</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A140" s="5">
         <v>62</v>
       </c>
@@ -15077,7 +15077,7 @@
         <v>3630</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A141" s="5">
         <v>63</v>
       </c>
@@ -15097,7 +15097,7 @@
         <v>3715</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A142" s="5">
         <v>64</v>
       </c>
@@ -15117,7 +15117,7 @@
         <v>3720</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A143" s="5">
         <v>65</v>
       </c>
@@ -15137,7 +15137,7 @@
         <v>3758</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A144" s="5">
         <v>66</v>
       </c>
@@ -15157,7 +15157,7 @@
         <v>3801</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A145" s="5">
         <v>67</v>
       </c>
@@ -15177,7 +15177,7 @@
         <v>3806</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A146" s="5">
         <v>68</v>
       </c>
@@ -15197,7 +15197,7 @@
         <v>3853</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A147" s="5">
         <v>69</v>
       </c>
@@ -15217,7 +15217,7 @@
         <v>3864</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A148" s="5">
         <v>70</v>
       </c>
@@ -15237,7 +15237,7 @@
         <v>3959</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A149" s="5">
         <v>71</v>
       </c>
